--- a/Docs/Test-Report/Test_Execution_Report_API.xlsx
+++ b/Docs/Test-Report/Test_Execution_Report_API.xlsx
@@ -1,26 +1,370 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\New folder\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB2952C-EA2F-4FD2-A426-24270E482E49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12540" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HƯỚNG DẪN" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Summary</t>
+  </si>
+  <si>
+    <t>Status Code Kỳ vọng</t>
+  </si>
+  <si>
+    <t>Status Code Thực tế</t>
+  </si>
+  <si>
+    <t>Bug ID (nếu Fail)</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>SECURITY - AUTHENTICATION</t>
+  </si>
+  <si>
+    <t>TC-AUTH-01</t>
+  </si>
+  <si>
+    <t>Đăng ký tài khoản với role MANAGER (kiểm tra lỗ hổng bảo mật)</t>
+  </si>
+  <si>
+    <t>Hệ thống PHẢI từ chối tạo tài khoản với role tự chọn, hoặc tự động ép role về "ROLE_CUSTOMER".
+(Thực tế: hệ thống chấp nhận role do client gửi - LỖ HỔNG BẢO MẬT đã xác nhận) (NFR-SEC-01)</t>
+  </si>
+  <si>
+    <t>PRODUCT &amp; CATEGORY - AUTHORIZATION</t>
+  </si>
+  <si>
+    <t>TC-AUTH-02</t>
+  </si>
+  <si>
+    <t>Truy cập API tạo sản phẩm mới khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-PROD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-03</t>
+  </si>
+  <si>
+    <t>Tạo sản phẩm mới bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden (Customer không có quyền tạo sản phẩm). (REQ-PROD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-04</t>
+  </si>
+  <si>
+    <t>Tạo sản phẩm mới bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden (chỉ Manager được tạo sản phẩm mới - Employee sửa được nhưng KHÔNG tạo được). (REQ-PROD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-26</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Tạo sản phẩm mới bằng tài khoản Manager với productId chưa tồn tại</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 200 OK, sản phẩm mới được tạo thành công trong DB. (REQ-PROD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-05</t>
+  </si>
+  <si>
+    <t>Truy cập API sửa sản phẩm khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-PROD-05)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-06</t>
+  </si>
+  <si>
+    <t>Sửa thông tin sản phẩm bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden. (REQ-PROD-05)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-24</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Sửa sản phẩm bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 200 OK, sản phẩm được cập nhật thành công (xác nhận Employee ĐƯỢC PHÉP sửa). (REQ-PROD-05)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-25</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Sửa sản phẩm bằng tài khoản Manager</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 200 OK, sản phẩm được cập nhật thành công. (REQ-PROD-05)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-07</t>
+  </si>
+  <si>
+    <t>Truy cập API xóa sản phẩm khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-PROD-06)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-08</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden. (REQ-PROD-06)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-09</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden (chỉ Manager được xóa sản phẩm). (REQ-PROD-06)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-27</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Xóa sản phẩm bằng tài khoản Manager</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 200 OK, sản phẩm bị xóa khỏi DB thành công. (REQ-PROD-06)</t>
+  </si>
+  <si>
+    <t>CART - AUTHORIZATION</t>
+  </si>
+  <si>
+    <t>TC-AUTH-10</t>
+  </si>
+  <si>
+    <t>Xem giỏ hàng khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-11</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ hàng bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden (giỏ hàng chỉ dành cho Customer). (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-12</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ hàng bằng tài khoản Manager</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-28</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Thêm sản phẩm vào giỏ hàng bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về true (200 OK), sản phẩm được thêm vào giỏ hàng. (REQ-CART-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-13</t>
+  </si>
+  <si>
+    <t>Gọi API Checkout (đặt hàng) khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-CART-05)</t>
+  </si>
+  <si>
+    <t>ORDER - AUTHORIZATION</t>
+  </si>
+  <si>
+    <t>TC-AUTH-14</t>
+  </si>
+  <si>
+    <t>Xem danh sách đơn hàng khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-ORD-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-19</t>
+  </si>
+  <si>
+    <t>Customer xem danh sách đơn hàng - xác nhận CHỈ thấy đơn của chính mình</t>
+  </si>
+  <si>
+    <t>Status 200. Response CHỈ chứa đơn hàng có buyerEmail = email của Customer đang đăng nhập, KHÔNG lẫn đơn của Customer khác. (REQ-ORD-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-15</t>
+  </si>
+  <si>
+    <t>Xem chi tiết đơn hàng của người khác (Customer A xem đơn của Customer B)</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized (đã xác nhận từ code OrderController.show() - luôn luôn 401, không có nhánh 403). (REQ-ORD-02)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-16</t>
+  </si>
+  <si>
+    <t>Hủy đơn hàng của người khác (Customer A hủy đơn của Customer B)</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized (đã xác nhận từ code OrderController.cancel() - luôn luôn 401, không có nhánh 403). (REQ-ORD-03)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-17</t>
+  </si>
+  <si>
+    <t>Xác nhận hoàn tất đơn hàng khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-ORD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-18</t>
+  </si>
+  <si>
+    <t>Xác nhận hoàn tất đơn hàng bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 403 Forbidden (bị chặn ở tầng Security Filter trước khi vào Controller). (REQ-ORD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-29</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Xác nhận hoàn tất đơn hàng bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 200 OK, đơn hàng chuyển sang trạng thái Completed. (REQ-ORD-04)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-30</t>
+  </si>
+  <si>
+    <t>[POSITIVE] Xác nhận hoàn tất đơn hàng bằng tài khoản Manager</t>
+  </si>
+  <si>
+    <t>PROFILE - AUTHORIZATION</t>
+  </si>
+  <si>
+    <t>TC-AUTH-20</t>
+  </si>
+  <si>
+    <t>Truy cập xem hồ sơ cá nhân khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-PROF-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-21</t>
+  </si>
+  <si>
+    <t>Truy cập cập nhật hồ sơ cá nhân khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 401 Unauthorized. (REQ-PROF-02)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-22</t>
+  </si>
+  <si>
+    <t>Customer A xem hồ sơ của Customer B (vi phạm quyền sở hữu)</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 400 Bad Request (KHÔNG phải 401/403 - đây là hành vi thật của code). (REQ-PROF-01)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-23</t>
+  </si>
+  <si>
+    <t>Customer A sửa hồ sơ với email trong body là của Customer B</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về 400 Bad Request (KHÔNG phải 401/403 - đây là hành vi thật của code). (REQ-PROF-02)</t>
+  </si>
+  <si>
+    <t>HƯỚNG DẪN ĐIỀN FILE NÀY</t>
+  </si>
+  <si>
+    <t>Assignee: E</t>
+  </si>
+  <si>
+    <t>1. Chạy Postman Collection qua Newman (`newman run ... -r cli,htmlextra`).</t>
+  </si>
+  <si>
+    <t>2. Mở report HTML vừa xuất (postman/newman-report/), đối chiếu từng request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   với đúng Test Case ID tương ứng trong file này.</t>
+  </si>
+  <si>
+    <t>3. Cột 'Kết quả': ghi OK/NG. Cột 'Status Code Thực tế': ghi mã HTTP thật nhận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   được (vd 200, 401, 403, 500) để so sánh trực tiếp với cột 'Status Code Kỳ vọng'.</t>
+  </si>
+  <si>
+    <t>4. Nếu Status Code Thực tế KHÁC Kỳ vọng -&gt; NG -&gt; bắt buộc điền Bug ID.</t>
+  </si>
+  <si>
+    <t>5. File report HTML gốc của Newman vẫn giữ nguyên trong postman/newman-report/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   làm bằng chứng gốc - file Excel này chỉ là bảng tổng hợp dễ đọc hơn.</t>
+  </si>
+  <si>
+    <t>Kết quả (Newman lần đầu)</t>
+  </si>
+  <si>
+    <t>Kết quả (Retest)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +372,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +413,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -79,44 +470,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +534,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +568,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +579,817 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>